--- a/AAII_Financials/Yearly/VCISY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VCISY_YR_FIN.xlsx
@@ -715,25 +715,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>88883400</v>
+        <v>87977000</v>
       </c>
       <c r="E8" s="3">
-        <v>75337000</v>
+        <v>74470400</v>
       </c>
       <c r="F8" s="3">
-        <v>77246600</v>
+        <v>76384400</v>
       </c>
       <c r="G8" s="3">
-        <v>66809900</v>
+        <v>66179300</v>
       </c>
       <c r="H8" s="3">
-        <v>57125000</v>
+        <v>56458500</v>
       </c>
       <c r="I8" s="3">
-        <v>53967000</v>
+        <v>53115600</v>
       </c>
       <c r="J8" s="3">
-        <v>54932100</v>
+        <v>54147700</v>
       </c>
       <c r="K8" s="3">
         <v>50783100</v>
@@ -781,25 +781,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>15789600</v>
+        <v>14883200</v>
       </c>
       <c r="E10" s="3">
-        <v>13260200</v>
+        <v>12393600</v>
       </c>
       <c r="F10" s="3">
-        <v>10672000</v>
+        <v>9809900</v>
       </c>
       <c r="G10" s="3">
-        <v>8598900</v>
+        <v>7968400</v>
       </c>
       <c r="H10" s="3">
-        <v>7743700</v>
+        <v>7077200</v>
       </c>
       <c r="I10" s="3">
-        <v>5920500</v>
+        <v>5069100</v>
       </c>
       <c r="J10" s="3">
-        <v>8882300</v>
+        <v>8097900</v>
       </c>
       <c r="K10" s="3">
         <v>7008200</v>
@@ -973,25 +973,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>78241200</v>
+        <v>77334700</v>
       </c>
       <c r="E17" s="3">
-        <v>66439600</v>
+        <v>65573000</v>
       </c>
       <c r="F17" s="3">
-        <v>68366300</v>
+        <v>67504100</v>
       </c>
       <c r="G17" s="3">
-        <v>59908100</v>
+        <v>59277500</v>
       </c>
       <c r="H17" s="3">
-        <v>52061900</v>
+        <v>51395400</v>
       </c>
       <c r="I17" s="3">
-        <v>50716800</v>
+        <v>49865400</v>
       </c>
       <c r="J17" s="3">
-        <v>48803700</v>
+        <v>48019300</v>
       </c>
       <c r="K17" s="3">
         <v>45277100</v>
